--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,260 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pitea</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,19 +881,19 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
         <v>1.14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
@@ -896,13 +896,13 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
@@ -1080,7 +1080,261 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -1111,46 +1111,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.25</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.84</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,11 +1159,11 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.47</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
@@ -1273,58 +1273,58 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,28 +881,28 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.13</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,72 +1022,72 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,72 +1097,72 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Beijing Tech FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,55 +1276,55 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,1785 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shenzhen 2028</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hangzhou Linping Wuyue</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jiangxi Lushan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ganzhou Ruishi FC</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wenzhou Professional</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Wuhan Three Towns II</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chengdu Rongcheng II</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Guangzhou Alpha</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gagra</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Samgurali Tskaltubo</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pitea</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1398,7 +1398,7 @@
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1906,7 +1906,7 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2139,34 +2139,34 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.02</v>
       </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2889,52 +2889,52 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.48</v>
@@ -2943,88 +2943,88 @@
         <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
         <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>1.01</v>
@@ -3051,58 +3051,58 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.37</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.37</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.37</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -884,13 +884,13 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1670,7 +1670,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.45</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2650,7 +2650,7 @@
         <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2889,178 +2889,178 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
         <v>40</v>
       </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14</v>
       </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,34 +3069,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1144,19 +1144,19 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1398,19 +1398,19 @@
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1661,16 +1661,16 @@
         <v>1.53</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.02</v>
@@ -1912,13 +1912,13 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.45</v>
@@ -2169,10 +2169,10 @@
         <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.29</v>
@@ -2420,13 +2420,13 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.62</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
@@ -2919,34 +2919,34 @@
         <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
         <v>27</v>
@@ -2955,10 +2955,10 @@
         <v>70</v>
       </c>
       <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2967,10 +2967,10 @@
         <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
@@ -2979,76 +2979,76 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.45</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,55 +1022,55 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1144,13 +1144,13 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,55 +1276,55 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.11</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1527,58 +1527,58 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.05</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.53</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
         <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1781,58 +1781,58 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1873,46 +1873,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.17</v>
+        <v>2.52</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,55 +2038,55 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.87</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,55 +2292,55 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,55 +2546,55 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.53</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
@@ -2683,10 +2683,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2889,76 +2889,76 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2967,91 +2967,91 @@
         <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
         <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>1.26</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>1.13</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>1.26</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.26</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>1.13</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>1.26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4</v>
+        <v>1.19</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>1.13</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>1.09</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>1.13</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>1.13</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.1</v>
+        <v>1.19</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI10" t="n">
         <v>2.78</v>
@@ -3060,13 +3060,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.6</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,166 +857,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>1.67</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1144,13 +1144,13 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -1365,178 +1365,178 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.47</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
         <v>2.24</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,13 +1548,13 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -1619,178 +1619,178 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,13 +1802,13 @@
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -1879,208 +1879,208 @@
         <v>2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
         <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
         <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
         <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -2127,220 +2127,220 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
         <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO7" t="n">
         <v>4.8</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>1.44</v>
       </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="n">
         <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>18</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>
@@ -2889,76 +2889,76 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2967,106 +2967,106 @@
         <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="n">
         <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.26</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.08</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.13</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.26</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.26</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.13</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.26</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.26</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.19</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.13</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.13</v>
+        <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.13</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.13</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.19</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>6.6</v>
@@ -3096,13 +3096,13 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 10:10:04</t>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,13 +917,13 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -944,91 +944,91 @@
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
         <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AW2" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
         <v>4.5</v>
       </c>
       <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BA2" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,37 +1040,37 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -1389,13 +1389,13 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
         <v>2.38</v>
@@ -1410,13 +1410,13 @@
         <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1497,7 +1497,7 @@
         <v>2.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AY4" t="n">
         <v>3.85</v>
@@ -1512,7 +1512,7 @@
         <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
         <v>2.86</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1667,10 +1667,10 @@
         <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1709,10 +1709,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1721,64 +1721,64 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.25</v>
       </c>
-      <c r="AY5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1894,10 +1894,10 @@
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.58</v>
@@ -1921,13 +1921,13 @@
         <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
@@ -1984,55 +1984,55 @@
         <v>2.98</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BC6" t="n">
         <v>4</v>
       </c>
-      <c r="BA6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BD6" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BE6" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.68</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -2145,7 +2145,7 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2181,16 +2181,16 @@
         <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7" t="n">
         <v>7.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
         <v>13</v>
@@ -2208,7 +2208,7 @@
         <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -2235,7 +2235,7 @@
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.8</v>
@@ -2244,55 +2244,55 @@
         <v>4.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>2.88</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -2405,58 +2405,58 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2468,10 +2468,10 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
         <v>40</v>
@@ -2480,121 +2480,121 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO8" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS8" t="n">
         <v>5</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AV8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="AU8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="BB8" t="n">
         <v>5.2</v>
       </c>
-      <c r="AW8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5.1</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5</v>
-      </c>
       <c r="BH8" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>1.43</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -2635,178 +2635,178 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2858,261 +2858,1023 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Richmond Kickers</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G10" t="n">
+        <v>990</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I10" t="n">
+        <v>990</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Miami FC</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Orange County Blues</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.46</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>3.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>3.55</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.06</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="N11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.39</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="W11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X11" t="n">
         <v>17</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y11" t="n">
         <v>18</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z11" t="n">
         <v>27</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA11" t="n">
         <v>70</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD11" t="n">
         <v>950</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE11" t="n">
         <v>46</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF11" t="n">
         <v>16</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG11" t="n">
         <v>12</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH11" t="n">
         <v>950</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI11" t="n">
         <v>70</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ11" t="n">
         <v>36</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK11" t="n">
         <v>27</v>
       </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AL11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM11" t="n">
         <v>120</v>
       </c>
-      <c r="AN10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
         <v>44</v>
       </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AP11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AQ11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BH11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>8</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BT11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ10" t="n">
+      <c r="BZ11" t="n">
         <v>0</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CA11" t="n">
         <v>0</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-23 12:17:29</t>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AV Alta FC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Westchester SC</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H2" t="n">
         <v>2.98</v>
       </c>
       <c r="I2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
@@ -884,13 +884,13 @@
         <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>1.51</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -905,10 +905,10 @@
         <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,13 +917,13 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -950,7 +950,7 @@
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
         <v>80</v>
@@ -965,58 +965,58 @@
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="BH2" t="n">
         <v>4.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1114,31 +1114,31 @@
         <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1401,7 +1401,7 @@
         <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
         <v>4.7</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
         <v>2.98</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.42</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1727,46 +1727,46 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
@@ -1775,7 +1775,7 @@
         <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
         <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
         <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
         <v>2.74</v>
@@ -1924,10 +1924,10 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
@@ -1939,7 +1939,7 @@
         <v>95</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1963,130 +1963,130 @@
         <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
         <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.6</v>
+        <v>16.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
@@ -2193,7 +2193,7 @@
         <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -2202,7 +2202,7 @@
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
         <v>34</v>
@@ -2211,7 +2211,7 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
@@ -2235,58 +2235,58 @@
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AT7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BC7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AY7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
         <v>2.88</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2411,40 +2411,40 @@
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
@@ -2456,7 +2456,7 @@
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2468,10 +2468,10 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
         <v>40</v>
@@ -2480,13 +2480,13 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
@@ -2495,25 +2495,25 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2522,28 +2522,28 @@
         <v>4.4</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="BI8" t="n">
         <v>3.1</v>
@@ -2552,49 +2552,49 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.43</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
@@ -2665,19 +2665,19 @@
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
@@ -2695,7 +2695,7 @@
         <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2746,55 +2746,55 @@
         <v>2.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="AR9" t="n">
         <v>2.46</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AU9" t="n">
         <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AW9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA9" t="n">
         <v>2.46</v>
       </c>
-      <c r="AX9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BB9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC9" t="n">
         <v>2.34</v>
       </c>
-      <c r="BC9" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BD9" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BE9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG9" t="n">
         <v>2.46</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.44</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2806,7 +2806,7 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -2889,112 +2889,112 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>1.27</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -3045,74 +3045,74 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
         <v>2.46</v>
@@ -3152,46 +3152,46 @@
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.55</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.69</v>
@@ -3206,7 +3206,7 @@
         <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
@@ -3233,7 +3233,7 @@
         <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
@@ -3242,25 +3242,25 @@
         <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -3272,49 +3272,49 @@
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.4</v>
       </c>
       <c r="BA11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB11" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BH11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK11" t="n">
         <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3350,13 +3350,13 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -3651,109 +3651,109 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.18</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3807,7 +3807,7 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
@@ -3816,13 +3816,13 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,25 +3834,25 @@
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -878,13 +878,13 @@
         <v>1.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
         <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
         <v>1.51</v>
@@ -899,16 +899,16 @@
         <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,16 +917,16 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -947,7 +947,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
@@ -959,67 +959,67 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>75</v>
       </c>
       <c r="AP2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV2" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
         <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="BI2" t="n">
         <v>2.22</v>
@@ -1028,49 +1028,49 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
         <v>1.16</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>44</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,13 +1159,13 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1407,7 +1407,7 @@
         <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
         <v>1.64</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="AT4" t="n">
         <v>2.98</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>2.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>2.94</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4</v>
-      </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>7.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1643,7 +1643,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
@@ -1652,13 +1652,13 @@
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>2.16</v>
@@ -1685,10 +1685,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC5" t="n">
         <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>950</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1709,10 +1709,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1721,64 +1721,64 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.15</v>
       </c>
-      <c r="AV5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1915,40 +1915,40 @@
         <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
         <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
         <v>970</v>
@@ -1963,7 +1963,7 @@
         <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
         <v>50</v>
@@ -1978,61 +1978,61 @@
         <v>60</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
         <v>3.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BG6" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.68</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BN6" t="n">
         <v>16.5</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BT6" t="n">
         <v>970</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
@@ -2181,10 +2181,10 @@
         <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
         <v>14.5</v>
@@ -2196,7 +2196,7 @@
         <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -2205,7 +2205,7 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
         <v>23</v>
@@ -2235,58 +2235,58 @@
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AQ7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR7" t="n">
         <v>3.45</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BB7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH7" t="n">
         <v>2.88</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -2411,19 +2411,19 @@
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>1.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
         <v>2.14</v>
@@ -2438,7 +2438,7 @@
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
@@ -2495,58 +2495,58 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA8" t="n">
         <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC8" t="n">
         <v>4.6</v>
       </c>
       <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
       </c>
       <c r="BF8" t="n">
         <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2558,10 +2558,10 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
         <v>4.7</v>
@@ -2570,16 +2570,16 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.14</v>
+        <v>3.45</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU8" t="n">
         <v>4.5</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -2635,67 +2635,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="G9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2722,7 +2722,7 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>970</v>
@@ -2734,131 +2734,131 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AT9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
         <v>2.32</v>
       </c>
-      <c r="AU9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AW9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.32</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.3</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
         <v>2.34</v>
       </c>
-      <c r="BD9" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BE9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.55</v>
+        <v>1.94</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2901,7 +2901,7 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2913,16 +2913,16 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.5</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -3176,31 +3176,31 @@
         <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
         <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z11" t="n">
         <v>27</v>
@@ -3209,31 +3209,31 @@
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
@@ -3245,118 +3245,118 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
         <v>12.5</v>
       </c>
       <c r="AR11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS11" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
         <v>4.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH11" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,72 +3383,72 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AV Alta FC</t>
+          <t>Loudoun United FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>2.68</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3613,14 +3613,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -3637,244 +3637,498 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AV Alta FC</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:39:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Spokane Velocity FC</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Westchester SC</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="F14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
         <v>6.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L14" t="n">
         <v>1.33</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1.05</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="N14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.24</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="P14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="S14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.1</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V14" t="n">
         <v>1.18</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X14" t="n">
         <v>22</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y14" t="n">
         <v>24</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z14" t="n">
         <v>50</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD14" t="n">
         <v>24</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE14" t="n">
         <v>75</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG14" t="n">
         <v>12</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AH14" t="n">
         <v>22</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI14" t="n">
         <v>75</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AJ14" t="n">
         <v>21</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK14" t="n">
         <v>20</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL14" t="n">
         <v>36</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7</v>
       </c>
-      <c r="BG13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
         <v>3.15</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
         <v>7.4</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
         <v>3.6</v>
       </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>8.6</v>
       </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>17.5</v>
       </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
         <v>6.8</v>
       </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>13</v>
       </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-23 16:32:01</t>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
@@ -908,7 +908,7 @@
         <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,7 +917,7 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>75</v>
@@ -935,7 +935,7 @@
         <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -965,58 +965,58 @@
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
         <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX2" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
         <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1111,28 +1111,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>2.8</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>44</v>
+        <v>2.46</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>1.25</v>
@@ -1144,7 +1144,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1159,118 +1159,118 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y3" t="n">
         <v>950</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.51</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1425,22 +1425,22 @@
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,91 +1452,91 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.75</v>
+        <v>1.72</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.96</v>
+        <v>1.89</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.98</v>
+        <v>1.77</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>1.66</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.76</v>
+        <v>1.78</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>1.72</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.76</v>
+        <v>1.77</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>1.71</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.96</v>
+        <v>1.88</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.96</v>
+        <v>1.81</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,13 +1548,13 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1649,10 +1649,10 @@
         <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1664,13 +1664,13 @@
         <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,106 +1679,106 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.05</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AZ5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.25</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BE5" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BF5" t="n">
         <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>2.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
         <v>3.95</v>
@@ -1888,7 +1888,7 @@
         <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1906,7 +1906,7 @@
         <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,7 +1915,7 @@
         <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.68</v>
@@ -1924,22 +1924,22 @@
         <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1948,7 +1948,7 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>970</v>
@@ -1960,79 +1960,79 @@
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.68</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -2181,43 +2181,43 @@
         <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF7" t="n">
         <v>34</v>
       </c>
-      <c r="AB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>40</v>
-      </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>95</v>
@@ -2226,67 +2226,67 @@
         <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.88</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -2405,34 +2405,34 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
         <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2444,49 +2444,49 @@
         <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI8" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
@@ -2495,10 +2495,10 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
         <v>9.199999999999999</v>
@@ -2510,37 +2510,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="n">
         <v>3.55</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
@@ -2674,37 +2674,37 @@
         <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
         <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2713,10 +2713,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
@@ -2725,13 +2725,13 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2743,16 +2743,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2761,10 +2761,10 @@
         <v>8.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.32</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
         <v>8.800000000000001</v>
@@ -2785,16 +2785,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BF9" t="n">
         <v>3.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -2889,76 +2889,76 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2973,28 +2973,28 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK10" t="n">
         <v>24</v>
       </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -3045,16 +3045,16 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -3152,13 +3152,13 @@
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.55</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -3173,16 +3173,16 @@
         <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.74</v>
@@ -3191,16 +3191,16 @@
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
         <v>27</v>
@@ -3212,10 +3212,10 @@
         <v>11.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
@@ -3230,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
         <v>36</v>
@@ -3248,7 +3248,7 @@
         <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
         <v>12</v>
@@ -3260,7 +3260,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -3272,7 +3272,7 @@
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
         <v>4.8</v>
@@ -3293,16 +3293,16 @@
         <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K12" t="n">
         <v>6.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,34 +3421,34 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -3651,112 +3651,112 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.76</v>
-      </c>
       <c r="X13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y13" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13</v>
-      </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP13" t="n">
         <v>1.03</v>
@@ -3807,10 +3807,10 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3941,13 +3941,13 @@
         <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
         <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -3971,7 +3971,7 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
         <v>2.88</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
@@ -899,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
         <v>1.75</v>
@@ -935,7 +935,7 @@
         <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -965,7 +965,7 @@
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>3.95</v>
@@ -977,19 +977,19 @@
         <v>3.65</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
         <v>3.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
         <v>4</v>
@@ -1022,7 +1022,7 @@
         <v>2.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1046,7 +1046,7 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="I3" t="n">
         <v>2.46</v>
@@ -1126,7 +1126,7 @@
         <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,10 +1135,10 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="O3" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
@@ -1159,7 +1159,7 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
         <v>1.23</v>
@@ -1168,7 +1168,7 @@
         <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="n">
         <v>500</v>
@@ -1183,7 +1183,7 @@
         <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1219,52 +1219,52 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AT3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AW3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BF3" t="n">
         <v>1.55</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
         <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
         <v>1.51</v>
@@ -1401,22 +1401,22 @@
         <v>2.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1455,7 +1455,7 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
         <v>500</v>
@@ -1473,58 +1473,58 @@
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.77</v>
+        <v>2.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.72</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.77</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1634,10 +1634,10 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1670,10 +1670,10 @@
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1727,16 +1727,16 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>4.3</v>
@@ -1745,40 +1745,40 @@
         <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>4.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.88</v>
       </c>
       <c r="BF5" t="n">
         <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -1915,16 +1915,16 @@
         <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
         <v>4.9</v>
@@ -2136,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J7" t="n">
         <v>3.05</v>
@@ -2160,13 +2160,13 @@
         <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -2175,7 +2175,7 @@
         <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W7" t="n">
         <v>1.25</v>
@@ -2226,10 +2226,10 @@
         <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
         <v>27</v>
@@ -2250,7 +2250,7 @@
         <v>5.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
@@ -2262,10 +2262,10 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
         <v>7.8</v>
@@ -2286,7 +2286,7 @@
         <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
         <v>2.88</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>970</v>
@@ -2447,10 +2447,10 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
@@ -2462,22 +2462,22 @@
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL8" t="n">
         <v>500</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>290</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2489,112 +2489,112 @@
         <v>500</v>
       </c>
       <c r="AP8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
         <v>11</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AW8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.4</v>
+        <v>1.47</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.17</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -2889,31 +2889,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
         <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
@@ -2922,31 +2922,31 @@
         <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X10" t="n">
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
         <v>42</v>
@@ -2958,7 +2958,7 @@
         <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2991,16 +2991,16 @@
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -3009,34 +3009,34 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
@@ -3045,74 +3045,74 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP10" t="n">
         <v>14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
         <v>26</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -3158,7 +3158,7 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -3167,13 +3167,13 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>1.9</v>
@@ -3182,7 +3182,7 @@
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T11" t="n">
         <v>1.74</v>
@@ -3200,7 +3200,7 @@
         <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
         <v>27</v>
@@ -3215,7 +3215,7 @@
         <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
@@ -3254,13 +3254,13 @@
         <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -3269,10 +3269,10 @@
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,25 +3284,25 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
         <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.25</v>
@@ -3681,16 +3681,16 @@
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
@@ -3699,16 +3699,16 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
         <v>36</v>
@@ -3756,7 +3756,7 @@
         <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP13" t="n">
         <v>1.03</v>
@@ -3807,7 +3807,7 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3947,7 +3947,7 @@
         <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
         <v>2.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,73 +857,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K2" t="n">
         <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O2" t="n">
         <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
@@ -944,7 +944,7 @@
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>60</v>
@@ -953,124 +953,124 @@
         <v>48</v>
       </c>
       <c r="AL2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO2" t="n">
         <v>80</v>
       </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>75</v>
-      </c>
       <c r="AP2" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AS2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF2" t="n">
         <v>3.65</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BG2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
         <v>3.6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
         <v>3.8</v>
       </c>
-      <c r="BF2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1180,19 +1180,19 @@
         <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH3" t="n">
         <v>950</v>
@@ -1219,64 +1219,64 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.33</v>
+        <v>3.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.39</v>
+        <v>2.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.39</v>
+        <v>2.16</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU3" t="n">
         <v>1.04</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
         <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>950</v>
@@ -1431,10 +1431,10 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1443,10 +1443,10 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
@@ -1467,13 +1467,13 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.62</v>
+        <v>4.5</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,13 +1497,13 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY4" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1515,58 +1515,58 @@
         <v>3.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.82</v>
+        <v>2.54</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.76</v>
+        <v>2.52</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1625,58 +1625,58 @@
         <v>1.79</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1742,7 +1742,7 @@
         <v>4.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AY5" t="n">
         <v>4.9</v>
@@ -1763,22 +1763,22 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
         <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BH5" t="n">
         <v>5.3</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.08</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,31 +1802,31 @@
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -1888,49 +1888,49 @@
         <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
         <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1981,79 +1981,79 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6</v>
       </c>
-      <c r="AU6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.34</v>
+        <v>2.32</v>
       </c>
       <c r="BN6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BO6" t="n">
         <v>3.45</v>
@@ -2062,16 +2062,16 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.28</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.32</v>
+        <v>3.3</v>
       </c>
       <c r="BT6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BU6" t="n">
         <v>4</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.32</v>
+        <v>3.3</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I7" t="n">
         <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -2178,10 +2178,10 @@
         <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y7" t="n">
         <v>7.4</v>
@@ -2190,25 +2190,25 @@
         <v>12.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -2232,67 +2232,67 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR7" t="n">
         <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
@@ -2304,43 +2304,43 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.32</v>
+        <v>12</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT7" t="n">
         <v>4.8</v>
       </c>
-      <c r="BP7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BU7" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.22</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.65</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
@@ -2447,22 +2447,22 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2471,10 +2471,10 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2492,28 +2492,28 @@
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>8.4</v>
@@ -2522,79 +2522,79 @@
         <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="BF8" t="n">
         <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO8" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BT8" t="n">
         <v>5.6</v>
       </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BU8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G9" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.13</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.15</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
         <v>950</v>
@@ -2701,7 +2701,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
         <v>32</v>
@@ -2713,37 +2713,37 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
         <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.2</v>
@@ -2773,7 +2773,7 @@
         <v>6.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
         <v>4.2</v>
@@ -2788,13 +2788,13 @@
         <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="BF9" t="n">
         <v>3.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
         <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2913,37 +2913,37 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.45</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
         <v>18.5</v>
@@ -2955,7 +2955,7 @@
         <v>130</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2982,16 +2982,16 @@
         <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
         <v>90</v>
@@ -3036,7 +3036,7 @@
         <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
@@ -3045,28 +3045,28 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
         <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
@@ -3084,35 +3084,35 @@
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G11" t="n">
         <v>2.44</v>
@@ -3152,22 +3152,22 @@
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
         <v>1.33</v>
@@ -3176,13 +3176,13 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
         <v>1.74</v>
@@ -3191,10 +3191,10 @@
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
         <v>17.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
         <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,25 +3421,25 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3693,7 +3693,7 @@
         <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>2.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3905,67 +3905,67 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
         <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3977,28 +3977,28 @@
         <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
       </c>
       <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>22</v>
       </c>
-      <c r="AI14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>21</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>20</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
@@ -4010,7 +4010,7 @@
         <v>10.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
@@ -4064,13 +4064,13 @@
         <v>7</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4088,13 +4088,13 @@
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4106,19 +4106,19 @@
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y2" t="n">
         <v>970</v>
       </c>
-      <c r="Y2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
         <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA2" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="BB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
         <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.52</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,40 +1037,40 @@
         <v>150</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
         <v>2.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Z3" t="n">
         <v>55</v>
@@ -1177,10 +1177,10 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>44</v>
@@ -1195,7 +1195,7 @@
         <v>500</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>600</v>
@@ -1219,70 +1219,70 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="AV3" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AW3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,37 +1294,37 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1431,7 +1431,7 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>16.5</v>
@@ -1443,7 +1443,7 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
         <v>500</v>
@@ -1467,13 +1467,13 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,13 +1497,13 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AY4" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1515,22 +1515,22 @@
         <v>3.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,13 +1542,13 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1560,13 +1560,13 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
         <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,25 +1685,25 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC5" t="n">
-        <v>14</v>
-      </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
         <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1712,7 +1712,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,67 +1721,67 @@
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD5" t="n">
         <v>7</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5</v>
-      </c>
       <c r="BE5" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="BI5" t="n">
         <v>2.4</v>
@@ -1790,16 +1790,16 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO5" t="n">
         <v>3.2</v>
@@ -1808,31 +1808,31 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1873,52 +1873,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
         <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
         <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T6" t="n">
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
@@ -1927,7 +1927,7 @@
         <v>1.62</v>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1939,7 +1939,7 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1984,109 +1984,109 @@
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA6" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BB6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.62</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BT6" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
         <v>2.08</v>
@@ -2139,25 +2139,25 @@
         <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
         <v>2.48</v>
@@ -2181,7 +2181,7 @@
         <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
         <v>7.4</v>
@@ -2214,13 +2214,13 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
         <v>120</v>
@@ -2232,61 +2232,61 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
         <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
       </c>
       <c r="AW7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX7" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.84</v>
@@ -2298,13 +2298,13 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>7.6</v>
@@ -2316,31 +2316,31 @@
         <v>44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
         <v>3.65</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>42</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2381,91 +2381,91 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.5</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2474,7 +2474,7 @@
         <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,7 +2483,7 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>500</v>
@@ -2492,109 +2492,109 @@
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>8.4</v>
       </c>
       <c r="AW8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.82</v>
+        <v>2.52</v>
       </c>
       <c r="BT8" t="n">
         <v>5.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.41</v>
       </c>
       <c r="G9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -2647,10 +2647,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1.23</v>
@@ -2665,13 +2665,13 @@
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
         <v>2.1</v>
@@ -2680,7 +2680,7 @@
         <v>1.68</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -2713,10 +2713,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
@@ -2725,16 +2725,16 @@
         <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
         <v>6.2</v>
@@ -2743,7 +2743,7 @@
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.2</v>
@@ -2773,7 +2773,7 @@
         <v>6.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA9" t="n">
         <v>4.2</v>
@@ -2788,77 +2788,77 @@
         <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="BF9" t="n">
         <v>3.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.94</v>
+        <v>3.95</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.71</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.3</v>
       </c>
-      <c r="I10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X10" t="n">
         <v>16</v>
@@ -2979,28 +2979,28 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -3009,35 +3009,35 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>15</v>
       </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16</v>
-      </c>
       <c r="BD10" t="n">
         <v>1.03</v>
       </c>
@@ -3045,74 +3045,74 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3149,10 +3149,10 @@
         <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
@@ -3176,34 +3176,34 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R11" t="n">
         <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
         <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
         <v>65</v>
@@ -3215,10 +3215,10 @@
         <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF11" t="n">
         <v>17</v>
@@ -3227,7 +3227,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
@@ -3242,13 +3242,13 @@
         <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
         <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
         <v>12</v>
@@ -3260,19 +3260,19 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB11" t="n">
         <v>5.4</v>
@@ -3293,10 +3293,10 @@
         <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
@@ -3305,58 +3305,58 @@
         <v>5.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3397,118 +3397,118 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>5.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
         <v>2.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -3517,34 +3517,34 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -3553,22 +3553,22 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,40 +3577,40 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
         <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
         <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3711,34 +3711,34 @@
         <v>19</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
         <v>24</v>
@@ -3753,10 +3753,10 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>1.03</v>
@@ -3816,13 +3816,13 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,47 +3834,47 @@
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
@@ -3920,7 +3920,7 @@
         <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3932,7 +3932,7 @@
         <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
         <v>2.16</v>
@@ -3944,22 +3944,22 @@
         <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
         <v>24</v>
@@ -3983,7 +3983,7 @@
         <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
@@ -3995,10 +3995,10 @@
         <v>70</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>900</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="AJ2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>530</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>990</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>60</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1111,82 +1111,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
         <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
@@ -1213,82 +1213,82 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,31 +1300,31 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
@@ -1431,10 +1431,10 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
@@ -1443,22 +1443,22 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH4" t="n">
         <v>500</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1467,16 +1467,16 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,70 +1497,70 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.36</v>
+        <v>7</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.44</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.18</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,13 +1572,13 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1622,58 +1622,58 @@
         <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>29</v>
@@ -1685,25 +1685,25 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1712,82 +1712,82 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>290</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>7</v>
       </c>
-      <c r="AW5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
         <v>5.9</v>
@@ -1796,43 +1796,43 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
         <v>4.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>10</v>
       </c>
-      <c r="BU5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
         <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.64</v>
@@ -1897,19 +1897,19 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
         <v>6.2</v>
@@ -1918,10 +1918,10 @@
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.62</v>
@@ -1930,7 +1930,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1945,7 +1945,7 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1978,61 +1978,61 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AW6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.62</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -2172,28 +2172,28 @@
         <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>9.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
@@ -2202,13 +2202,13 @@
         <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -2220,37 +2220,37 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
         <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>7.6</v>
@@ -2259,37 +2259,37 @@
         <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI7" t="n">
         <v>2.5</v>
@@ -2298,25 +2298,25 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2325,22 +2325,22 @@
         <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
         <v>3.1</v>
@@ -2390,7 +2390,7 @@
         <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J8" t="n">
         <v>3.45</v>
@@ -2405,37 +2405,37 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
         <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
         <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>16</v>
@@ -2447,7 +2447,7 @@
         <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
         <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2489,16 +2489,16 @@
         <v>500</v>
       </c>
       <c r="AP8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
         <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2510,46 +2510,46 @@
         <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC8" t="n">
         <v>16.5</v>
       </c>
       <c r="BD8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
         <v>7.2</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.64</v>
+        <v>5.2</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>5.6</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
         <v>32</v>
@@ -2713,10 +2713,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
@@ -2725,10 +2725,10 @@
         <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2740,13 +2740,13 @@
         <v>6.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
         <v>4.2</v>
@@ -2773,7 +2773,7 @@
         <v>6.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
         <v>4.2</v>
@@ -2788,34 +2788,34 @@
         <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
         <v>3.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BO9" t="n">
         <v>3.4</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.34</v>
+        <v>1.79</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
         <v>1.95</v>
@@ -2901,49 +2901,49 @@
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
         <v>18.5</v>
@@ -2964,7 +2964,7 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
         <v>13.5</v>
@@ -2973,34 +2973,34 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>23</v>
       </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>24</v>
-      </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -3009,10 +3009,10 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
         <v>14.5</v>
@@ -3021,22 +3021,22 @@
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
         <v>1.03</v>
@@ -3048,13 +3048,13 @@
         <v>9.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3066,25 +3066,25 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
         <v>3.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
@@ -3096,23 +3096,23 @@
         <v>42</v>
       </c>
       <c r="BW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BX10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
         <v>3.1</v>
@@ -3167,34 +3167,34 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>1.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
         <v>3.35</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
         <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
         <v>17.5</v>
@@ -3206,7 +3206,7 @@
         <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -3215,10 +3215,10 @@
         <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
         <v>17</v>
@@ -3227,10 +3227,10 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
         <v>36</v>
@@ -3260,19 +3260,19 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,34 +3284,34 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC11" t="n">
         <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
         <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
         <v>5</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN11" t="n">
         <v>5.6</v>
@@ -3332,13 +3332,13 @@
         <v>19</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
         <v>32</v>
       </c>
       <c r="BS11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT11" t="n">
         <v>6.6</v>
@@ -3356,7 +3356,7 @@
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
         <v>70</v>
@@ -3598,7 +3598,7 @@
         <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3654,10 +3654,10 @@
         <v>1.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -3681,10 +3681,10 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
         <v>1.48</v>
@@ -3693,16 +3693,16 @@
         <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3941,10 +3941,10 @@
         <v>1.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
         <v>1.71</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>04:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Xian Chongde Ronghai</t>
+          <t>Beijing Tech FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Taian Tiankuang</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>6</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>820</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>930</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>530</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Beijing Tech FC</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shandong Taishan B</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.7</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>12.5</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.87</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF3" t="n">
         <v>970</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
         <v>11</v>
       </c>
-      <c r="AD3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>500</v>
-      </c>
       <c r="AH3" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AT3" t="n">
-        <v>2.18</v>
+        <v>3.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.28</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.32</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.32</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.8</v>
+        <v>160</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.6</v>
+        <v>1.15</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>1.12</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.2</v>
+        <v>1.13</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1356,112 +1356,112 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shenzhen 2028</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Ganzhou Ruishi FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
         <v>4.4</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
         <v>700</v>
@@ -1470,115 +1470,115 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
         <v>6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.12</v>
+        <v>170</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.17</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1610,73 +1610,73 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jiangxi Lushan</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ganzhou Ruishi FC</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>2.56</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.64</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.26</v>
-      </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,109 +1685,109 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="n">
         <v>160</v>
       </c>
-      <c r="AM5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7</v>
-      </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
         <v>5.9</v>
@@ -1799,25 +1799,25 @@
         <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
         <v>5.5</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>1.78</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Guangzhou Alpha</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I6" t="n">
         <v>2.42</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.9</v>
-      </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="T6" t="n">
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="W6" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO6" t="n">
         <v>6</v>
       </c>
-      <c r="AS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Guangzhou Alpha</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.35</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AW7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC7" t="n">
         <v>22</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BD7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.68</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X8" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>1.6</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X8" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="BZ8" t="n">
         <v>13</v>
       </c>
-      <c r="AH8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Portland Hearts of Pine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Richmond Kickers</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.23</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA9" t="n">
         <v>6.6</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,34 +2880,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Portland Hearts of Pine</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richmond Kickers</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2916,148 +2916,148 @@
         <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
         <v>5</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3134,229 +3134,229 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Loudoun United FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
         <v>36</v>
       </c>
-      <c r="AK11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>40</v>
       </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>36</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,132 +3383,132 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Loudoun United FC</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF12" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -3517,34 +3517,34 @@
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -3553,22 +3553,22 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="BP12" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>15</v>
       </c>
-      <c r="BT12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3637,39 +3637,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Spokane Velocity FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AV Alta FC</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3681,148 +3681,148 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
         <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
         <v>21</v>
       </c>
-      <c r="Y13" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI13" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG13" t="n">
         <v>40</v>
       </c>
-      <c r="AP13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,301 +3834,47 @@
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Spokane Velocity FC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Westchester SC</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>13</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>310</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.6</v>
       </c>
-      <c r="G2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>46</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="BD3" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="BE3" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>120</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S4" t="n">
+        <v>38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.72</v>
       </c>
-      <c r="H4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="X4" t="n">
         <v>3.1</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11</v>
-      </c>
       <c r="Y4" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>85</v>
       </c>
       <c r="AE4" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>370</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>420</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>360</v>
+      </c>
+      <c r="BE4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="BF4" t="n">
         <v>60</v>
       </c>
-      <c r="AI4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>310</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1605,234 +1605,234 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Guangzhou Alpha</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.15</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y5" t="n">
         <v>6.2</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>180</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>200</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>510</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>130</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>950</v>
       </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="BK5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>160</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN5" t="n">
+      <c r="BP5" t="n">
+        <v>230</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
         <v>5.4</v>
       </c>
-      <c r="BO5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>800</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.78</v>
+        <v>5.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1864,229 +1864,229 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Guangzhou Alpha</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="P6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.52</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.71</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>980</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>990</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>990</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>990</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>1.89</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BO6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>860</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BT6" t="n">
         <v>6</v>
       </c>
-      <c r="BP6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>870</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>1.69</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2127,100 +2127,100 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB7" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
         <v>290</v>
@@ -2232,34 +2232,34 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
         <v>14.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>8.6</v>
@@ -2268,79 +2268,79 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BB7" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
         <v>18.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
         <v>7.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI7" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU7" t="n">
         <v>5.4</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>6.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S8" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="X8" t="n">
         <v>950</v>
@@ -2441,7 +2441,7 @@
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2450,7 +2450,7 @@
         <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,7 +2459,7 @@
         <v>240</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
@@ -2471,22 +2471,22 @@
         <v>190</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>7.8</v>
@@ -2495,22 +2495,22 @@
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
         <v>6.2</v>
@@ -2522,7 +2522,7 @@
         <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2531,80 +2531,80 @@
         <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG8" t="n">
         <v>10.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP8" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="BZ8" t="n">
         <v>13</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -2668,13 +2668,13 @@
         <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
         <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
         <v>1.72</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.6</v>
@@ -2907,94 +2907,94 @@
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
         <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
         <v>17.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
         <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
         <v>17</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>21</v>
-      </c>
       <c r="AO10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
@@ -3006,10 +3006,10 @@
         <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>7.6</v>
@@ -3018,55 +3018,55 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
         <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
@@ -3075,16 +3075,16 @@
         <v>4.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
         <v>32</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>8.4</v>
@@ -3191,13 +3191,13 @@
         <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
         <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
         <v>38</v>
@@ -3215,16 +3215,16 @@
         <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
         <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
         <v>27</v>
@@ -3236,73 +3236,73 @@
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO11" t="n">
         <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF11" t="n">
         <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>70</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="n">
         <v>4.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
         <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3427,82 +3427,82 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
         <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP12" t="n">
         <v>1.03</v>
@@ -3553,16 +3553,16 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H13" t="n">
         <v>4.8</v>
@@ -3663,7 +3663,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -3675,25 +3675,25 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
         <v>2.14</v>
@@ -3702,7 +3702,7 @@
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3711,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3735,28 +3735,28 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>1.03</v>
@@ -3807,7 +3807,7 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
         <v>40</v>
@@ -3816,7 +3816,7 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3834,13 +3834,13 @@
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J2" t="n">
         <v>2.56</v>
       </c>
-      <c r="I2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR2" t="n">
         <v>3.75</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AS2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12</v>
       </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BC2" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>160</v>
       </c>
       <c r="BF2" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1135,206 +1135,206 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.15</v>
-      </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
         <v>240</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>190</v>
       </c>
       <c r="AJ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL3" t="n">
         <v>25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>790</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AO3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS3" t="n">
         <v>90</v>
       </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG3" t="n">
         <v>15</v>
       </c>
-      <c r="BF3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI3" t="n">
         <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.86</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>970</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW3" t="n">
         <v>11.5</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1404,7 +1404,7 @@
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
         <v>1.72</v>
@@ -1416,16 +1416,16 @@
         <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
@@ -1434,7 +1434,7 @@
         <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>22</v>
@@ -1443,7 +1443,7 @@
         <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1470,13 +1470,13 @@
         <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1485,34 +1485,34 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1521,7 +1521,7 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
         <v>42</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I5" t="n">
         <v>3.1</v>
@@ -1634,160 +1634,160 @@
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
         <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
         <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>55</v>
       </c>
-      <c r="AB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>36</v>
-      </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
         <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5" t="n">
         <v>4.9</v>
@@ -1799,37 +1799,37 @@
         <v>9.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO5" t="n">
         <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
         <v>6.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
         <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW5" t="n">
         <v>7.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY5" t="n">
         <v>8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.29</v>
@@ -1897,37 +1897,37 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y6" t="n">
         <v>38</v>
@@ -1936,79 +1936,79 @@
         <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
         <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>5.3</v>
@@ -2017,22 +2017,22 @@
         <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
         <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
@@ -2041,7 +2041,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
         <v>7.4</v>
@@ -2053,34 +2053,34 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BT6" t="n">
         <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -2154,86 +2154,86 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO7" t="n">
         <v>42</v>
       </c>
-      <c r="AF7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>34</v>
-      </c>
       <c r="AP7" t="n">
         <v>1.03</v>
       </c>
@@ -2283,13 +2283,13 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
         <v>3.2</v>
@@ -2304,13 +2304,13 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,19 +2328,19 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2393,52 +2393,52 @@
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
         <v>2.26</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -2447,43 +2447,43 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
         <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
         <v>65</v>
@@ -2504,7 +2504,7 @@
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
         <v>1.03</v>
@@ -2537,46 +2537,46 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>30</v>
       </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>32</v>
-      </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,19 +881,19 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>2.92</v>
@@ -905,37 +905,37 @@
         <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
         <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE2" t="n">
         <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -944,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
         <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="AN2" t="n">
         <v>11</v>
@@ -965,19 +965,19 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>15.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>48</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>7.8</v>
@@ -986,19 +986,19 @@
         <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
         <v>16.5</v>
@@ -1007,10 +1007,10 @@
         <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
         <v>8.800000000000001</v>
@@ -1019,68 +1019,68 @@
         <v>29</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>13</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR2" t="n">
         <v>26</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>8.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BV2" t="n">
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>46</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>20</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1111,199 +1111,199 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
         <v>15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC3" t="n">
         <v>24</v>
       </c>
-      <c r="AA3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>23</v>
-      </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS3" t="n">
         <v>9.4</v>
@@ -1312,16 +1312,16 @@
         <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW3" t="n">
         <v>8.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
         <v>9.800000000000001</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1365,145 +1365,145 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>230</v>
+        <v>980</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
         <v>16</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO4" t="n">
         <v>110</v>
       </c>
       <c r="AP4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
         <v>42</v>
@@ -1512,52 +1512,52 @@
         <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS4" t="n">
         <v>14.5</v>
@@ -1566,7 +1566,7 @@
         <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1643,142 +1643,142 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK5" t="n">
         <v>27</v>
       </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
         <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="n">
         <v>4.1</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.65</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
         <v>4.8</v>
@@ -1894,7 +1894,7 @@
         <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
         <v>4.9</v>
@@ -1906,13 +1906,13 @@
         <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
         <v>1.72</v>
@@ -1927,10 +1927,10 @@
         <v>2.3</v>
       </c>
       <c r="X6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
         <v>95</v>
@@ -1939,10 +1939,10 @@
         <v>190</v>
       </c>
       <c r="AB6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
         <v>27</v>
@@ -1951,7 +1951,7 @@
         <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1966,46 +1966,46 @@
         <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO6" t="n">
         <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
         <v>7.4</v>
@@ -2017,22 +2017,22 @@
         <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH6" t="n">
         <v>4.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -860,227 +860,227 @@
         <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.5</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>48</v>
+        <v>1.37</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>1.37</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>1.37</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>1.37</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>1.37</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>1.37</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>1.37</v>
       </c>
       <c r="BC2" t="n">
-        <v>15.5</v>
+        <v>1.37</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>1.37</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>1.37</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="BG2" t="n">
-        <v>29</v>
+        <v>1.37</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>1.52</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>1.52</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>590</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="BP2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.4</v>
+        <v>1.53</v>
       </c>
       <c r="BR2" t="n">
-        <v>26</v>
+        <v>910</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>1.52</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.6</v>
+        <v>690</v>
       </c>
       <c r="BU2" t="n">
-        <v>7</v>
+        <v>1.52</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>1.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="BZ2" t="n">
-        <v>20</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>1.52</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1102,229 +1102,229 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County Blues</t>
+          <t>Loudoun United FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.54</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>1.23</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>16.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>1.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>990</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>990</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>1.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BC3" t="n">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BF3" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>910</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1351,234 +1351,234 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:33:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Loudoun United FC</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>960</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>960</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7.2</v>
       </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10</v>
       </c>
-      <c r="AT4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>3.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>3.45</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>3.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>3.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>3.75</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>48</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>36</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>34</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1643,206 +1643,206 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
         <v>120</v>
       </c>
       <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AW5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE5" t="n">
         <v>12</v>
       </c>
-      <c r="AD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>27</v>
       </c>
-      <c r="AL5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>22</v>
-      </c>
       <c r="BH5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>65</v>
+        <v>2.42</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>18</v>
+        <v>2.68</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>22</v>
+        <v>2.72</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>27</v>
+        <v>2.78</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
@@ -1897,13 +1897,13 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
         <v>1.62</v>
@@ -1912,154 +1912,154 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Z6" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
         <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>18</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
         <v>36</v>
       </c>
       <c r="AX6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>30</v>
       </c>
-      <c r="BB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BH6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ6" t="n">
         <v>8.199999999999999</v>
@@ -2071,32 +2071,32 @@
         <v>16.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>28</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>30</v>
-      </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Portland Hearts of Pine</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Richmond Kickers</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.4</v>
       </c>
-      <c r="I2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="U2" t="n">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>990</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP2" t="n">
         <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>10</v>
       </c>
-      <c r="AR2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.37</v>
+        <v>170</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.37</v>
+        <v>44</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.37</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.37</v>
+        <v>160</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.37</v>
+        <v>14</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.37</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.37</v>
+        <v>140</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Spokane Velocity FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Loudoun United FC</t>
+          <t>Westchester SC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.23</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>16.5</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>2.54</v>
       </c>
       <c r="J3" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1135,968 +1135,206 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1000</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>26</v>
-      </c>
       <c r="AC3" t="n">
-        <v>990</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>990</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>990</v>
+        <v>8.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>990</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.04</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.17</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.04</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.04</v>
+        <v>25</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.04</v>
+        <v>22</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL3" t="n">
         <v>960</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR3" t="n">
-        <v>910</v>
+        <v>25</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:33:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Orange County Blues</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>960</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>960</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-24 20:24:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AV Alta FC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-24 20:24:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Spokane Velocity FC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Westchester SC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>12</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
